--- a/Docs/QA-Testing/RTM.xlsx
+++ b/Docs/QA-Testing/RTM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\repo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\repo\moi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88010CE-4A29-4ECF-BCAF-489CD7B0006A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51DEFC3-C966-415E-A863-831188A41EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="7560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="113">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -214,15 +214,9 @@
     <t>API</t>
   </si>
   <si>
-    <t>(cần thêm TC đăng ký role=MANAGER)</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
-    <t>(nên tạo ticket mới hoặc map BUG-01 cũ)</t>
-  </si>
-  <si>
     <t>TC-USER-07, TC-USER-10</t>
   </si>
   <si>
@@ -359,6 +353,12 @@
   </si>
   <si>
     <t>TC_FE_EMP_08→10, TC_FE_MRG_08→10</t>
+  </si>
+  <si>
+    <t>SCRUM-58</t>
+  </si>
+  <si>
+    <t>TC-SEC-01</t>
   </si>
 </sst>
 </file>
@@ -731,9 +731,10 @@
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="8" width="23.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.25">
+    <row r="1" spans="1:9" ht="31.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -845,7 +846,7 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="94.5">
+    <row r="5" spans="1:9" ht="15.75">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -862,14 +863,14 @@
         <v>63</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75">
@@ -889,13 +890,13 @@
         <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="I6" s="2"/>
     </row>
@@ -916,13 +917,13 @@
         <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I7" s="2"/>
     </row>
@@ -931,10 +932,10 @@
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -943,13 +944,13 @@
         <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="I8" s="2"/>
     </row>
@@ -958,10 +959,10 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -970,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>46</v>
@@ -985,10 +986,10 @@
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>60</v>
@@ -997,25 +998,25 @@
         <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="47.25">
+    <row r="11" spans="1:9" ht="31.5">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -1024,16 +1025,16 @@
         <v>23</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="31.5">
@@ -1044,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -1053,7 +1054,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>26</v>
@@ -1062,7 +1063,7 @@
         <v>55</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="31.5">
@@ -1073,7 +1074,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>60</v>
@@ -1082,10 +1083,10 @@
         <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>46</v>
@@ -1097,7 +1098,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>30</v>
@@ -1109,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>55</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="31.5">
@@ -1126,7 +1127,7 @@
         <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>30</v>
@@ -1138,7 +1139,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>32</v>
@@ -1153,7 +1154,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>30</v>
@@ -1165,7 +1166,7 @@
         <v>7</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -1180,7 +1181,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>30</v>
@@ -1189,10 +1190,10 @@
         <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>36</v>
@@ -1207,7 +1208,7 @@
         <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>30</v>
@@ -1219,22 +1220,22 @@
         <v>7</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="47.25">
+    <row r="19" spans="1:9" ht="31.5">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>39</v>
@@ -1246,7 +1247,7 @@
         <v>7</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>40</v>
@@ -1255,7 +1256,7 @@
         <v>46</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75">
@@ -1263,7 +1264,7 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>39</v>
@@ -1275,10 +1276,10 @@
         <v>7</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>46</v>
@@ -1302,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>44</v>
@@ -1317,7 +1318,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>39</v>
@@ -1329,10 +1330,10 @@
         <v>7</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>46</v>

--- a/Docs/QA-Testing/RTM.xlsx
+++ b/Docs/QA-Testing/RTM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\repo\moi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\sp3\dasua\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51DEFC3-C966-415E-A863-831188A41EAA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BB164B-D125-4900-A35D-684431D20F14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="7560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="118">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -359,6 +359,21 @@
   </si>
   <si>
     <t>TC-SEC-01</t>
+  </si>
+  <si>
+    <t>REQ-ORD-05</t>
+  </si>
+  <si>
+    <t>Chặn chuyển trạng thái đơn hàng không hợp lệ</t>
+  </si>
+  <si>
+    <t>TC-ST-03, TC-ST-04, TC-ST-05</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SCRUM-59</t>
   </si>
 </sst>
 </file>
@@ -375,25 +390,28 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="13"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="163"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +421,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,16 +464,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -720,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -734,7 +776,7 @@
     <col min="9" max="9" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5">
+    <row r="1" spans="1:9" ht="33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +805,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="31.5">
+    <row r="2" spans="1:9" ht="33">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -792,7 +834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5">
+    <row r="3" spans="1:9" ht="33">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -821,7 +863,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="31.5">
+    <row r="4" spans="1:9" ht="33">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -846,7 +888,7 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="15.75">
+    <row r="5" spans="1:9" ht="16.5">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -873,61 +915,61 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:9" ht="33">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75">
-      <c r="A7" s="2" t="s">
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="33">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="31.5">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="33">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -954,7 +996,7 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="31.5">
+    <row r="9" spans="1:9" ht="33">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -981,7 +1023,7 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="31.5">
+    <row r="10" spans="1:9" ht="33">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1008,7 +1050,7 @@
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="31.5">
+    <row r="11" spans="1:9" ht="49.5">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -1021,7 +1063,7 @@
       <c r="D11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1037,7 +1079,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="31.5">
+    <row r="12" spans="1:9" ht="33">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1066,7 +1108,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="31.5">
+    <row r="13" spans="1:9" ht="33">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1079,7 +1121,7 @@
       <c r="D13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1093,144 +1135,144 @@
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="31.5">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:9" ht="33">
+      <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="31.5">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" ht="33">
+      <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="31.5">
-      <c r="A16" s="2" t="s">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="33">
+      <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="31.5">
-      <c r="A17" s="2" t="s">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="33">
+      <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="31.5">
-      <c r="A18" s="2" t="s">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="33">
+      <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="31.5">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" ht="33">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1259,7 +1301,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75">
+    <row r="20" spans="1:9" ht="33">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -1286,7 +1328,7 @@
       </c>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75">
+    <row r="21" spans="1:9" ht="33">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -1313,7 +1355,7 @@
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="31.5">
+    <row r="22" spans="1:9" ht="33">
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
@@ -1339,6 +1381,35 @@
         <v>46</v>
       </c>
       <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="33">
+      <c r="A23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/QA-Testing/RTM.xlsx
+++ b/Docs/QA-Testing/RTM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\MouseWithoutBorders\sp3\dasua\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BB164B-D125-4900-A35D-684431D20F14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C0424D-7F93-C14E-B174-17AC98FCE003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10200" windowHeight="7560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="125">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -374,13 +374,34 @@
   </si>
   <si>
     <t>SCRUM-59</t>
+  </si>
+  <si>
+    <t>Tình trạng vá</t>
+  </si>
+  <si>
+    <t>PATCHED</t>
+  </si>
+  <si>
+    <t>Người thực hiện</t>
+  </si>
+  <si>
+    <t>THANH</t>
+  </si>
+  <si>
+    <t>THÙY</t>
+  </si>
+  <si>
+    <t>THÀNH</t>
+  </si>
+  <si>
+    <t>THANH, THÙY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,21 +783,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
     <col min="7" max="7" width="42" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33">
+    <row r="1" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,8 +827,14 @@
       <c r="I1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="33">
+      <c r="J1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -833,8 +862,14 @@
       <c r="I2" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="33">
+      <c r="J2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -862,8 +897,14 @@
       <c r="I3" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="33">
+      <c r="J3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -887,8 +928,10 @@
         <v>46</v>
       </c>
       <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="16.5">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -914,8 +957,14 @@
       <c r="I5" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="33">
+      <c r="J5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
@@ -941,8 +990,10 @@
         <v>67</v>
       </c>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" ht="33">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -968,8 +1019,10 @@
         <v>67</v>
       </c>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" ht="33">
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -995,8 +1048,10 @@
         <v>73</v>
       </c>
       <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" ht="33">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1022,8 +1077,10 @@
         <v>46</v>
       </c>
       <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" ht="33">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -1049,8 +1106,10 @@
         <v>67</v>
       </c>
       <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" ht="49.5">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -1078,8 +1137,14 @@
       <c r="I11" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="33">
+      <c r="J11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -1107,8 +1172,14 @@
       <c r="I12" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="33">
+      <c r="J12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1134,8 +1205,10 @@
         <v>46</v>
       </c>
       <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="33">
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>29</v>
       </c>
@@ -1163,8 +1236,14 @@
       <c r="I14" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="33">
+      <c r="J14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>31</v>
       </c>
@@ -1190,8 +1269,10 @@
         <v>46</v>
       </c>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" ht="33">
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -1217,8 +1298,10 @@
         <v>46</v>
       </c>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" ht="33">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
@@ -1244,8 +1327,10 @@
         <v>46</v>
       </c>
       <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" ht="33">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
@@ -1271,8 +1356,10 @@
         <v>46</v>
       </c>
       <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" ht="33">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -1300,8 +1387,14 @@
       <c r="I19" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="33">
+      <c r="J19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>41</v>
       </c>
@@ -1327,8 +1420,10 @@
         <v>46</v>
       </c>
       <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" ht="33">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>42</v>
       </c>
@@ -1354,8 +1449,10 @@
         <v>46</v>
       </c>
       <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="33">
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="36" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>45</v>
       </c>
@@ -1381,8 +1478,10 @@
         <v>46</v>
       </c>
       <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="33">
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>113</v>
       </c>
@@ -1409,6 +1508,12 @@
       </c>
       <c r="I23" s="5" t="s">
         <v>117</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
